--- a/Apostas_Diarias/Apostas_20260426.xlsx
+++ b/Apostas_Diarias/Apostas_20260426.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_2B590F4F9516CD24AD80CBF05035A8705DB7FD9E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D400BB7D-FACC-4053-AC82-6FB79B74DB2A}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="11_2B590F4F95A64213E500CBF050A568B07FADE99E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{693D8CBE-D698-4CEB-82DD-062D97F1B5D4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="48">
   <si>
     <t>Data</t>
   </si>
@@ -74,55 +74,94 @@
     <t>P1 ⭐</t>
   </si>
   <si>
+    <t>04:30:00</t>
+  </si>
+  <si>
+    <t>CHINA 1</t>
+  </si>
+  <si>
+    <t>Changchun Yatai x Guangdong GZ-Power FC</t>
+  </si>
+  <si>
+    <t>Lay_CS_0x1_B365</t>
+  </si>
+  <si>
+    <t>06:00:00</t>
+  </si>
+  <si>
+    <t>Qingdao Hainiu x Shandong Taishan</t>
+  </si>
+  <si>
+    <t>07:00:00</t>
+  </si>
+  <si>
+    <t>PORTUGAL 2</t>
+  </si>
+  <si>
+    <t>Lusitania Futebol Clube x Pacos Ferreira</t>
+  </si>
+  <si>
+    <t>07:15:00</t>
+  </si>
+  <si>
+    <t>POLAND 1</t>
+  </si>
+  <si>
+    <t>Wisla Plock x Radomiak Radom</t>
+  </si>
+  <si>
+    <t>08:30:00</t>
+  </si>
+  <si>
+    <t>TURKEY 1</t>
+  </si>
+  <si>
+    <t>Genclerbirligi x Kocaelispor</t>
+  </si>
+  <si>
     <t>09:00:00</t>
   </si>
   <si>
+    <t>Henan Songshan Longmen x Shanghai Shenhua</t>
+  </si>
+  <si>
     <t>DENMARK 1</t>
   </si>
   <si>
     <t>Silkeborg x Randers</t>
   </si>
   <si>
-    <t>Lay_CS_0x1_B365</t>
-  </si>
-  <si>
-    <t>11:15:00</t>
-  </si>
-  <si>
-    <t>SPAIN 2</t>
-  </si>
-  <si>
-    <t>Granada x Almeria</t>
+    <t>10:30:00</t>
+  </si>
+  <si>
+    <t>BULGARIA 1</t>
+  </si>
+  <si>
+    <t>Lokomotiv Plovdiv x Cherno More</t>
   </si>
   <si>
     <t>11:30:00</t>
   </si>
   <si>
-    <t>SERBIA 1</t>
-  </si>
-  <si>
-    <t>FK Novi Pazar x Cukaricki</t>
-  </si>
-  <si>
-    <t>12:00:00</t>
-  </si>
-  <si>
-    <t>AUSTRIA 1</t>
-  </si>
-  <si>
-    <t>Sturm Graz x Austria Wien</t>
+    <t>SWEDEN 1</t>
+  </si>
+  <si>
+    <t>IFK Goteborg x GAIS</t>
   </si>
   <si>
     <t>12:30:00</t>
   </si>
   <si>
-    <t>SLOVENIA 1</t>
-  </si>
-  <si>
-    <t>NK Celje x NK Aluminij</t>
+    <t>SCOTLAND 1</t>
+  </si>
+  <si>
+    <t>Hibernian x Hearts</t>
   </si>
   <si>
     <t>13:00:00</t>
+  </si>
+  <si>
+    <t>Arda x Botev Plovdiv</t>
   </si>
   <si>
     <t>ITALY 1</t>
@@ -477,14 +516,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="29" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
@@ -527,6 +566,9 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
+      <c r="L1">
+        <v>500</v>
+      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -548,12 +590,14 @@
         <v>16</v>
       </c>
       <c r="G2">
-        <v>11</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="H2">
-        <v>11</v>
+        <f>G2</f>
+        <v>9.1999999999999993</v>
       </c>
       <c r="I2">
+        <f>$L$1</f>
         <v>500</v>
       </c>
       <c r="J2" t="str">
@@ -562,7 +606,7 @@
       </c>
       <c r="K2">
         <f>IF(L2=1,0.935/(H2-1)*I2,-500)</f>
-        <v>46.75</v>
+        <v>57.01219512195123</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -579,30 +623,32 @@
         <v>17</v>
       </c>
       <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
         <v>18</v>
       </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
       <c r="F3" t="s">
         <v>16</v>
       </c>
       <c r="G3">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="H3">
-        <v>11</v>
+        <f t="shared" ref="H3:H14" si="0">G3</f>
+        <v>9.4</v>
       </c>
       <c r="I3">
+        <f t="shared" ref="I3:I14" si="1">$L$1</f>
         <v>500</v>
       </c>
       <c r="J3" t="str">
-        <f t="shared" ref="J3:J8" si="0">IF(L3=1,"GREEN","RED")</f>
+        <f t="shared" ref="J3:J14" si="2">IF(L3=1,"GREEN","RED")</f>
         <v>GREEN</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K8" si="1">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
-        <v>46.75</v>
+        <f t="shared" ref="K3:K14" si="3">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
+        <v>55.654761904761905</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -616,33 +662,35 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
         <v>20</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>21</v>
       </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
       <c r="F4" t="s">
         <v>16</v>
       </c>
       <c r="G4">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H4">
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>11</v>
       </c>
       <c r="I4">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>GREEN</v>
       </c>
       <c r="K4">
-        <f t="shared" si="1"/>
-        <v>35.96153846153846</v>
+        <f t="shared" si="3"/>
+        <v>46.75</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -656,36 +704,38 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
         <v>23</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>24</v>
       </c>
-      <c r="E5" t="s">
-        <v>25</v>
-      </c>
       <c r="F5" t="s">
         <v>16</v>
       </c>
       <c r="G5">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="H5">
-        <v>13.5</v>
+        <f t="shared" si="0"/>
+        <v>11</v>
       </c>
       <c r="I5">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J5" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
+        <f t="shared" si="2"/>
+        <v>RED</v>
       </c>
       <c r="K5">
-        <f t="shared" si="1"/>
-        <v>37.400000000000006</v>
+        <f t="shared" si="3"/>
+        <v>-500</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
@@ -696,33 +746,35 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
         <v>26</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>27</v>
       </c>
-      <c r="E6" t="s">
-        <v>28</v>
-      </c>
       <c r="F6" t="s">
         <v>16</v>
       </c>
       <c r="G6">
-        <v>65</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="H6">
-        <v>65</v>
+        <f t="shared" si="0"/>
+        <v>9.8000000000000007</v>
       </c>
       <c r="I6">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J6" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>GREEN</v>
       </c>
       <c r="K6">
-        <f t="shared" si="1"/>
-        <v>7.3046875</v>
+        <f t="shared" si="3"/>
+        <v>53.125</v>
       </c>
       <c r="L6">
         <v>1</v>
@@ -736,33 +788,35 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" t="s">
         <v>29</v>
       </c>
-      <c r="D7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" t="s">
-        <v>31</v>
-      </c>
       <c r="F7" t="s">
         <v>16</v>
       </c>
       <c r="G7">
-        <v>9.8000000000000007</v>
+        <v>11.5</v>
       </c>
       <c r="H7">
-        <v>9.8000000000000007</v>
+        <f t="shared" si="0"/>
+        <v>11.5</v>
       </c>
       <c r="I7">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J7" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>GREEN</v>
       </c>
       <c r="K7">
-        <f t="shared" si="1"/>
-        <v>53.125</v>
+        <f t="shared" si="3"/>
+        <v>44.523809523809526</v>
       </c>
       <c r="L7">
         <v>1</v>
@@ -773,38 +827,292 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
         <v>30</v>
       </c>
       <c r="E8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8">
+        <v>11</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="J8" t="str">
+        <f t="shared" si="2"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="3"/>
+        <v>46.75</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" t="s">
         <v>34</v>
       </c>
-      <c r="F8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8">
+      <c r="F9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9">
+        <v>11</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="J9" t="str">
+        <f t="shared" si="2"/>
+        <v>RED</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="3"/>
+        <v>-500</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10">
+        <v>11.5</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="0"/>
+        <v>11.5</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="J10" t="str">
+        <f t="shared" si="2"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="3"/>
+        <v>44.523809523809526</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11">
+        <v>11</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="J11" t="str">
+        <f t="shared" si="2"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="3"/>
+        <v>46.75</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12">
+        <v>9.4</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="0"/>
+        <v>9.4</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="J12" t="str">
+        <f t="shared" si="2"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="3"/>
+        <v>55.654761904761905</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="0"/>
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="J13" t="str">
+        <f t="shared" si="2"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="3"/>
+        <v>53.125</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14">
         <v>8.1999999999999993</v>
       </c>
-      <c r="H8">
+      <c r="H14">
+        <f t="shared" si="0"/>
         <v>8.1999999999999993</v>
       </c>
-      <c r="I8">
-        <v>500</v>
-      </c>
-      <c r="J8" t="str">
-        <f t="shared" si="0"/>
+      <c r="I14">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="J14" t="str">
+        <f t="shared" si="2"/>
         <v>GREEN</v>
       </c>
-      <c r="K8">
-        <f t="shared" si="1"/>
+      <c r="K14">
+        <f t="shared" si="3"/>
         <v>64.930555555555557</v>
       </c>
-      <c r="L8">
+      <c r="L14">
         <v>1</v>
       </c>
     </row>

--- a/Apostas_Diarias/Apostas_20260426.xlsx
+++ b/Apostas_Diarias/Apostas_20260426.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="11_2B590F4F95A64213E500CBF050A568B07FADE99E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{693D8CBE-D698-4CEB-82DD-062D97F1B5D4}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="11_2B590F4F9516CD24AD80CBF05035A8705DB7FD9E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D400BB7D-FACC-4053-AC82-6FB79B74DB2A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="35">
   <si>
     <t>Data</t>
   </si>
@@ -74,94 +74,55 @@
     <t>P1 ⭐</t>
   </si>
   <si>
-    <t>04:30:00</t>
-  </si>
-  <si>
-    <t>CHINA 1</t>
-  </si>
-  <si>
-    <t>Changchun Yatai x Guangdong GZ-Power FC</t>
+    <t>09:00:00</t>
+  </si>
+  <si>
+    <t>DENMARK 1</t>
+  </si>
+  <si>
+    <t>Silkeborg x Randers</t>
   </si>
   <si>
     <t>Lay_CS_0x1_B365</t>
   </si>
   <si>
-    <t>06:00:00</t>
-  </si>
-  <si>
-    <t>Qingdao Hainiu x Shandong Taishan</t>
-  </si>
-  <si>
-    <t>07:00:00</t>
-  </si>
-  <si>
-    <t>PORTUGAL 2</t>
-  </si>
-  <si>
-    <t>Lusitania Futebol Clube x Pacos Ferreira</t>
-  </si>
-  <si>
-    <t>07:15:00</t>
-  </si>
-  <si>
-    <t>POLAND 1</t>
-  </si>
-  <si>
-    <t>Wisla Plock x Radomiak Radom</t>
-  </si>
-  <si>
-    <t>08:30:00</t>
-  </si>
-  <si>
-    <t>TURKEY 1</t>
-  </si>
-  <si>
-    <t>Genclerbirligi x Kocaelispor</t>
-  </si>
-  <si>
-    <t>09:00:00</t>
-  </si>
-  <si>
-    <t>Henan Songshan Longmen x Shanghai Shenhua</t>
-  </si>
-  <si>
-    <t>DENMARK 1</t>
-  </si>
-  <si>
-    <t>Silkeborg x Randers</t>
-  </si>
-  <si>
-    <t>10:30:00</t>
-  </si>
-  <si>
-    <t>BULGARIA 1</t>
-  </si>
-  <si>
-    <t>Lokomotiv Plovdiv x Cherno More</t>
+    <t>11:15:00</t>
+  </si>
+  <si>
+    <t>SPAIN 2</t>
+  </si>
+  <si>
+    <t>Granada x Almeria</t>
   </si>
   <si>
     <t>11:30:00</t>
   </si>
   <si>
-    <t>SWEDEN 1</t>
-  </si>
-  <si>
-    <t>IFK Goteborg x GAIS</t>
+    <t>SERBIA 1</t>
+  </si>
+  <si>
+    <t>FK Novi Pazar x Cukaricki</t>
+  </si>
+  <si>
+    <t>12:00:00</t>
+  </si>
+  <si>
+    <t>AUSTRIA 1</t>
+  </si>
+  <si>
+    <t>Sturm Graz x Austria Wien</t>
   </si>
   <si>
     <t>12:30:00</t>
   </si>
   <si>
-    <t>SCOTLAND 1</t>
-  </si>
-  <si>
-    <t>Hibernian x Hearts</t>
+    <t>SLOVENIA 1</t>
+  </si>
+  <si>
+    <t>NK Celje x NK Aluminij</t>
   </si>
   <si>
     <t>13:00:00</t>
-  </si>
-  <si>
-    <t>Arda x Botev Plovdiv</t>
   </si>
   <si>
     <t>ITALY 1</t>
@@ -516,14 +477,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="40" customWidth="1"/>
+    <col min="5" max="5" width="29" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
@@ -566,9 +527,6 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1">
-        <v>500</v>
-      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -590,14 +548,12 @@
         <v>16</v>
       </c>
       <c r="G2">
-        <v>9.1999999999999993</v>
+        <v>11</v>
       </c>
       <c r="H2">
-        <f>G2</f>
-        <v>9.1999999999999993</v>
+        <v>11</v>
       </c>
       <c r="I2">
-        <f>$L$1</f>
         <v>500</v>
       </c>
       <c r="J2" t="str">
@@ -606,7 +562,7 @@
       </c>
       <c r="K2">
         <f>IF(L2=1,0.935/(H2-1)*I2,-500)</f>
-        <v>57.01219512195123</v>
+        <v>46.75</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -623,32 +579,30 @@
         <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
       </c>
       <c r="G3">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="H3">
-        <f t="shared" ref="H3:H14" si="0">G3</f>
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="I3">
-        <f t="shared" ref="I3:I14" si="1">$L$1</f>
         <v>500</v>
       </c>
       <c r="J3" t="str">
-        <f t="shared" ref="J3:J14" si="2">IF(L3=1,"GREEN","RED")</f>
+        <f t="shared" ref="J3:J8" si="0">IF(L3=1,"GREEN","RED")</f>
         <v>GREEN</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K14" si="3">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
-        <v>55.654761904761905</v>
+        <f t="shared" ref="K3:K8" si="1">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
+        <v>46.75</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -662,35 +616,33 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
       </c>
       <c r="G4">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H4">
+        <v>14</v>
+      </c>
+      <c r="I4">
+        <v>500</v>
+      </c>
+      <c r="J4" t="str">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="I4">
+        <v>GREEN</v>
+      </c>
+      <c r="K4">
         <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J4" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K4">
-        <f t="shared" si="3"/>
-        <v>46.75</v>
+        <v>35.96153846153846</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -704,38 +656,36 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
       </c>
       <c r="G5">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="H5">
+        <v>13.5</v>
+      </c>
+      <c r="I5">
+        <v>500</v>
+      </c>
+      <c r="J5" t="str">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="I5">
+        <v>GREEN</v>
+      </c>
+      <c r="K5">
         <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J5" t="str">
-        <f t="shared" si="2"/>
-        <v>RED</v>
-      </c>
-      <c r="K5">
-        <f t="shared" si="3"/>
-        <v>-500</v>
+        <v>37.400000000000006</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
@@ -746,35 +696,33 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
       </c>
       <c r="G6">
-        <v>9.8000000000000007</v>
+        <v>65</v>
       </c>
       <c r="H6">
+        <v>65</v>
+      </c>
+      <c r="I6">
+        <v>500</v>
+      </c>
+      <c r="J6" t="str">
         <f t="shared" si="0"/>
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="I6">
+        <v>GREEN</v>
+      </c>
+      <c r="K6">
         <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J6" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K6">
-        <f t="shared" si="3"/>
-        <v>53.125</v>
+        <v>7.3046875</v>
       </c>
       <c r="L6">
         <v>1</v>
@@ -788,35 +736,33 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s">
         <v>16</v>
       </c>
       <c r="G7">
-        <v>11.5</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="H7">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="I7">
+        <v>500</v>
+      </c>
+      <c r="J7" t="str">
         <f t="shared" si="0"/>
-        <v>11.5</v>
-      </c>
-      <c r="I7">
+        <v>GREEN</v>
+      </c>
+      <c r="K7">
         <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J7" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K7">
-        <f t="shared" si="3"/>
-        <v>44.523809523809526</v>
+        <v>53.125</v>
       </c>
       <c r="L7">
         <v>1</v>
@@ -827,292 +773,38 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
         <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
       </c>
       <c r="G8">
-        <v>11</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="H8">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="I8">
+        <v>500</v>
+      </c>
+      <c r="J8" t="str">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="I8">
+        <v>GREEN</v>
+      </c>
+      <c r="K8">
         <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J8" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K8">
-        <f t="shared" si="3"/>
-        <v>46.75</v>
+        <v>64.930555555555557</v>
       </c>
       <c r="L8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9">
-        <v>11</v>
-      </c>
-      <c r="H9">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="I9">
-        <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J9" t="str">
-        <f t="shared" si="2"/>
-        <v>RED</v>
-      </c>
-      <c r="K9">
-        <f t="shared" si="3"/>
-        <v>-500</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10">
-        <v>11.5</v>
-      </c>
-      <c r="H10">
-        <f t="shared" si="0"/>
-        <v>11.5</v>
-      </c>
-      <c r="I10">
-        <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J10" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K10">
-        <f t="shared" si="3"/>
-        <v>44.523809523809526</v>
-      </c>
-      <c r="L10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11">
-        <v>11</v>
-      </c>
-      <c r="H11">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="I11">
-        <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J11" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K11">
-        <f t="shared" si="3"/>
-        <v>46.75</v>
-      </c>
-      <c r="L11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" t="s">
-        <v>33</v>
-      </c>
-      <c r="E12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12">
-        <v>9.4</v>
-      </c>
-      <c r="H12">
-        <f t="shared" si="0"/>
-        <v>9.4</v>
-      </c>
-      <c r="I12">
-        <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J12" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K12">
-        <f t="shared" si="3"/>
-        <v>55.654761904761905</v>
-      </c>
-      <c r="L12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" t="s">
-        <v>43</v>
-      </c>
-      <c r="E13" t="s">
-        <v>44</v>
-      </c>
-      <c r="F13" t="s">
-        <v>16</v>
-      </c>
-      <c r="G13">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="H13">
-        <f t="shared" si="0"/>
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="I13">
-        <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J13" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K13">
-        <f t="shared" si="3"/>
-        <v>53.125</v>
-      </c>
-      <c r="L13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" t="s">
-        <v>47</v>
-      </c>
-      <c r="F14" t="s">
-        <v>16</v>
-      </c>
-      <c r="G14">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="H14">
-        <f t="shared" si="0"/>
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="I14">
-        <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J14" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K14">
-        <f t="shared" si="3"/>
-        <v>64.930555555555557</v>
-      </c>
-      <c r="L14">
         <v>1</v>
       </c>
     </row>
